--- a/TestData/Data.xlsx
+++ b/TestData/Data.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\SA_Automation_2025_2\SeleniumMaven\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9514B7B4-03D5-4DA5-8556-E298DA93A163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5EEA38-AB81-4AA6-A2F7-61F1D03EE248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="userdata" sheetId="1" r:id="rId1"/>
+    <sheet name="Bookdata" sheetId="2" r:id="rId2"/>
+    <sheet name="HRM" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>UserName</t>
   </si>
@@ -55,13 +57,46 @@
   </si>
   <si>
     <t>amit123</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AuthorName</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>CoreJava</t>
+  </si>
+  <si>
+    <t>Priyanka</t>
+  </si>
+  <si>
+    <t>Selenium</t>
+  </si>
+  <si>
+    <t>Mukesh</t>
+  </si>
+  <si>
+    <t>TestNg</t>
+  </si>
+  <si>
+    <t>Naveen</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +122,20 @@
     <font>
       <b/>
       <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,11 +177,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,4 +514,106 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BAAE8E-FE9F-42D5-8FA5-0D1AB18AA2AF}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="25.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4">
+        <v>800</v>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3583178B-291B-4FB9-85F6-C6D8A8952CD9}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="4" width="32.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TestData/Data.xlsx
+++ b/TestData/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\SA_Automation_2025_2\SeleniumMaven\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5EEA38-AB81-4AA6-A2F7-61F1D03EE248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C900871D-46A3-4DBA-B7A0-C0E830FC400C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>UserName</t>
   </si>
@@ -90,13 +90,25 @@
   </si>
   <si>
     <t>password</t>
+  </si>
+  <si>
+    <t>Raj</t>
+  </si>
+  <si>
+    <t>raj123</t>
+  </si>
+  <si>
+    <t>Sumit</t>
+  </si>
+  <si>
+    <t>sumit123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +153,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -177,13 +197,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,18 +611,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3583178B-291B-4FB9-85F6-C6D8A8952CD9}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="32.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:2" s="3" customFormat="1" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -610,6 +631,54 @@
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
     </row>

--- a/TestData/Data.xlsx
+++ b/TestData/Data.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\SA_Automation_2025_2\HybridFramework\TestData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51623C06-9A80-4223-8538-A18128C50AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="UserData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,15 +24,60 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>standard_user</t>
+  </si>
+  <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>fn</t>
+  </si>
+  <si>
+    <t>Priyanka</t>
+  </si>
+  <si>
+    <t>ln</t>
+  </si>
+  <si>
+    <t>Nigade</t>
+  </si>
+  <si>
+    <t>pc</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +88,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,12 +96,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +412,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="31.2" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="34.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>411047</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TestData/Data.xlsx
+++ b/TestData/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trainings\SA_Automation_2025_2\HybridFramework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51623C06-9A80-4223-8538-A18128C50AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53A02F1-C46F-4053-8179-2090599C0921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>standard_user</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>pc</t>
+  </si>
+  <si>
+    <t>"411047"</t>
   </si>
 </sst>
 </file>
@@ -456,8 +459,8 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
-        <v>411047</v>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
